--- a/3_meta-analysis/data/sheets_for_analysis/xlsx/lachman_1.xlsx
+++ b/3_meta-analysis/data/sheets_for_analysis/xlsx/lachman_1.xlsx
@@ -531,16 +531,16 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>22</v>
+        <v>22.5</v>
       </c>
       <c r="G2" t="n">
-        <v>22</v>
+        <v>22.5</v>
       </c>
       <c r="H2" t="n">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="I2" t="n">
-        <v>19</v>
+        <v>19.5</v>
       </c>
       <c r="J2" t="n">
         <v>28.5</v>
@@ -569,10 +569,10 @@
         <v>36</v>
       </c>
       <c r="R2" t="n">
-        <v>0.189</v>
+        <v>0.192</v>
       </c>
       <c r="S2" t="n">
-        <v>0.7545185522000337</v>
+        <v>0.751</v>
       </c>
     </row>
     <row r="3">
@@ -598,16 +598,16 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>61</v>
+        <v>61.5</v>
       </c>
       <c r="G3" t="n">
-        <v>86</v>
+        <v>86.5</v>
       </c>
       <c r="H3" t="n">
-        <v>31</v>
+        <v>31.5</v>
       </c>
       <c r="I3" t="n">
-        <v>67</v>
+        <v>67.5</v>
       </c>
       <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
@@ -618,10 +618,10 @@
       <c r="P3" t="inlineStr"/>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="n">
-        <v>0.293</v>
+        <v>0.296</v>
       </c>
       <c r="S3" t="n">
-        <v>0.3648949847985844</v>
+        <v>0.364</v>
       </c>
     </row>
     <row r="4">
@@ -647,16 +647,16 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>32</v>
+        <v>32.5</v>
       </c>
       <c r="G4" t="n">
-        <v>33</v>
+        <v>33.5</v>
       </c>
       <c r="H4" t="n">
-        <v>14</v>
+        <v>14.5</v>
       </c>
       <c r="I4" t="n">
-        <v>17</v>
+        <v>17.5</v>
       </c>
       <c r="J4" t="n">
         <v>27.3</v>
@@ -685,10 +685,10 @@
         <v>24</v>
       </c>
       <c r="R4" t="n">
-        <v>0.732</v>
+        <v>0.737</v>
       </c>
       <c r="S4" t="n">
-        <v>0.4983047826339736</v>
+        <v>0.494</v>
       </c>
     </row>
     <row r="5">
@@ -714,16 +714,16 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>42</v>
+        <v>42.5</v>
       </c>
       <c r="G5" t="n">
-        <v>47</v>
+        <v>47.5</v>
       </c>
       <c r="H5" t="n">
-        <v>6</v>
+        <v>6.5</v>
       </c>
       <c r="I5" t="n">
-        <v>19</v>
+        <v>19.5</v>
       </c>
       <c r="J5" t="n">
         <v>25.8</v>
@@ -752,10 +752,10 @@
         <v>36</v>
       </c>
       <c r="R5" t="n">
-        <v>0.246</v>
+        <v>0.259</v>
       </c>
       <c r="S5" t="n">
-        <v>0.5317803203448757</v>
+        <v>0.518</v>
       </c>
     </row>
     <row r="6">
@@ -781,16 +781,16 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>45</v>
+        <v>45.5</v>
       </c>
       <c r="G6" t="n">
-        <v>32</v>
+        <v>32.5</v>
       </c>
       <c r="H6" t="n">
-        <v>16</v>
+        <v>16.5</v>
       </c>
       <c r="I6" t="n">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="J6" t="n">
         <v>27</v>
@@ -819,10 +819,10 @@
         <v>84</v>
       </c>
       <c r="R6" t="n">
-        <v>0.806</v>
+        <v>0.801</v>
       </c>
       <c r="S6" t="n">
-        <v>0.4759594672775561</v>
+        <v>0.471</v>
       </c>
     </row>
     <row r="7">
@@ -848,16 +848,16 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>31</v>
+        <v>31.5</v>
       </c>
       <c r="G7" t="n">
-        <v>31</v>
+        <v>31.5</v>
       </c>
       <c r="H7" t="n">
-        <v>9</v>
+        <v>9.5</v>
       </c>
       <c r="I7" t="n">
-        <v>9</v>
+        <v>9.5</v>
       </c>
       <c r="J7" t="n">
         <v>25.2</v>
@@ -889,7 +889,7 @@
         <v>1</v>
       </c>
       <c r="S7" t="n">
-        <v>0.5595813731096785</v>
+        <v>0.549</v>
       </c>
     </row>
     <row r="8">
@@ -915,16 +915,16 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>37</v>
+        <v>37.5</v>
       </c>
       <c r="G8" t="n">
-        <v>37</v>
+        <v>37.5</v>
       </c>
       <c r="H8" t="n">
-        <v>8</v>
+        <v>8.5</v>
       </c>
       <c r="I8" t="n">
-        <v>6</v>
+        <v>6.5</v>
       </c>
       <c r="J8" t="n">
         <v>0</v>
@@ -953,10 +953,10 @@
         <v>60.6</v>
       </c>
       <c r="R8" t="n">
-        <v>1.425</v>
+        <v>1.398</v>
       </c>
       <c r="S8" t="n">
-        <v>0.5986714372704659</v>
+        <v>0.582</v>
       </c>
     </row>
     <row r="9">
@@ -982,16 +982,16 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>40</v>
+        <v>40.5</v>
       </c>
       <c r="G9" t="n">
-        <v>46</v>
+        <v>46.5</v>
       </c>
       <c r="H9" t="n">
-        <v>5</v>
+        <v>5.5</v>
       </c>
       <c r="I9" t="n">
-        <v>7</v>
+        <v>7.5</v>
       </c>
       <c r="J9" t="n">
         <v>22.3</v>
@@ -1020,10 +1020,10 @@
         <v>81</v>
       </c>
       <c r="R9" t="n">
-        <v>0.796</v>
+        <v>0.8169999999999999</v>
       </c>
       <c r="S9" t="n">
-        <v>0.6301345864730781</v>
+        <v>0.608</v>
       </c>
     </row>
     <row r="10">
@@ -1049,16 +1049,16 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>43</v>
+        <v>43.5</v>
       </c>
       <c r="G10" t="n">
-        <v>46</v>
+        <v>46.5</v>
       </c>
       <c r="H10" t="n">
-        <v>8</v>
+        <v>8.5</v>
       </c>
       <c r="I10" t="n">
-        <v>8</v>
+        <v>8.5</v>
       </c>
       <c r="J10" t="n">
         <v>0</v>
@@ -1090,7 +1090,7 @@
         <v>1.086</v>
       </c>
       <c r="S10" t="n">
-        <v>0.5521659334340654</v>
+        <v>0.539</v>
       </c>
     </row>
     <row r="11">
@@ -1116,16 +1116,16 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>24</v>
+        <v>24.5</v>
       </c>
       <c r="G11" t="n">
-        <v>23</v>
+        <v>23.5</v>
       </c>
       <c r="H11" t="n">
-        <v>8</v>
+        <v>8.5</v>
       </c>
       <c r="I11" t="n">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="J11" t="n">
         <v>29.8</v>
@@ -1154,10 +1154,10 @@
         <v>120</v>
       </c>
       <c r="R11" t="n">
-        <v>0.545</v>
+        <v>0.554</v>
       </c>
       <c r="S11" t="n">
-        <v>0.6014502674722361</v>
+        <v>0.592</v>
       </c>
     </row>
     <row r="12">
@@ -1183,16 +1183,16 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>32</v>
+        <v>32.5</v>
       </c>
       <c r="G12" t="n">
-        <v>32</v>
+        <v>32.5</v>
       </c>
       <c r="H12" t="n">
-        <v>6</v>
+        <v>6.5</v>
       </c>
       <c r="I12" t="n">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="J12" t="n">
         <v>29.8</v>
@@ -1221,10 +1221,10 @@
         <v>73.2</v>
       </c>
       <c r="R12" t="n">
-        <v>0.337</v>
+        <v>0.352</v>
       </c>
       <c r="S12" t="n">
-        <v>0.578517813899149</v>
+        <v>0.5649999999999999</v>
       </c>
     </row>
     <row r="13">
@@ -1250,16 +1250,16 @@
         </is>
       </c>
       <c r="F13" t="n">
-        <v>30</v>
+        <v>30.5</v>
       </c>
       <c r="G13" t="n">
-        <v>32</v>
+        <v>32.5</v>
       </c>
       <c r="H13" t="n">
-        <v>22</v>
+        <v>22.5</v>
       </c>
       <c r="I13" t="n">
-        <v>25</v>
+        <v>25.5</v>
       </c>
       <c r="J13" t="inlineStr"/>
       <c r="K13" t="inlineStr"/>
@@ -1270,10 +1270,10 @@
       <c r="P13" t="inlineStr"/>
       <c r="Q13" t="inlineStr"/>
       <c r="R13" t="n">
-        <v>0.77</v>
+        <v>0.772</v>
       </c>
       <c r="S13" t="n">
-        <v>0.5944002761706023</v>
+        <v>0.593</v>
       </c>
     </row>
     <row r="14">
@@ -1299,16 +1299,16 @@
         </is>
       </c>
       <c r="F14" t="n">
-        <v>14</v>
+        <v>14.5</v>
       </c>
       <c r="G14" t="n">
-        <v>38</v>
+        <v>38.5</v>
       </c>
       <c r="H14" t="n">
-        <v>4</v>
+        <v>4.5</v>
       </c>
       <c r="I14" t="n">
-        <v>6</v>
+        <v>6.5</v>
       </c>
       <c r="J14" t="n">
         <v>26.5</v>
@@ -1337,10 +1337,10 @@
         <v>12</v>
       </c>
       <c r="R14" t="n">
-        <v>2.133</v>
+        <v>2.215</v>
       </c>
       <c r="S14" t="n">
-        <v>0.7402139330400818</v>
+        <v>0.712</v>
       </c>
     </row>
     <row r="15">
@@ -1366,16 +1366,16 @@
         </is>
       </c>
       <c r="F15" t="n">
-        <v>18</v>
+        <v>18.5</v>
       </c>
       <c r="G15" t="n">
-        <v>21</v>
+        <v>21.5</v>
       </c>
       <c r="H15" t="n">
-        <v>4</v>
+        <v>4.5</v>
       </c>
       <c r="I15" t="n">
-        <v>5</v>
+        <v>5.5</v>
       </c>
       <c r="J15" t="n">
         <v>31</v>
@@ -1404,10 +1404,10 @@
         <v>24</v>
       </c>
       <c r="R15" t="n">
-        <v>0.914</v>
+        <v>0.9350000000000001</v>
       </c>
       <c r="S15" t="n">
-        <v>0.7641521912738138</v>
+        <v>0.733</v>
       </c>
     </row>
     <row r="16">
@@ -1433,16 +1433,16 @@
         </is>
       </c>
       <c r="F16" t="n">
-        <v>33</v>
+        <v>33.5</v>
       </c>
       <c r="G16" t="n">
-        <v>32</v>
+        <v>32.5</v>
       </c>
       <c r="H16" t="n">
-        <v>6</v>
+        <v>6.5</v>
       </c>
       <c r="I16" t="n">
-        <v>6</v>
+        <v>6.5</v>
       </c>
       <c r="J16" t="n">
         <v>25.8</v>
@@ -1474,7 +1474,7 @@
         <v>0.963</v>
       </c>
       <c r="S16" t="n">
-        <v>0.6393996471940759</v>
+        <v>0.619</v>
       </c>
     </row>
     <row r="17">
@@ -1500,16 +1500,16 @@
         </is>
       </c>
       <c r="F17" t="n">
-        <v>53</v>
+        <v>53.5</v>
       </c>
       <c r="G17" t="n">
-        <v>58</v>
+        <v>58.5</v>
       </c>
       <c r="H17" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="I17" t="n">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="J17" t="n">
         <v>25</v>
@@ -1538,10 +1538,10 @@
         <v>120</v>
       </c>
       <c r="R17" t="n">
-        <v>0.891</v>
+        <v>0.899</v>
       </c>
       <c r="S17" t="n">
-        <v>0.4778370828238473</v>
+        <v>0.469</v>
       </c>
     </row>
     <row r="18">
@@ -1567,16 +1567,16 @@
         </is>
       </c>
       <c r="F18" t="n">
-        <v>38</v>
+        <v>38.5</v>
       </c>
       <c r="G18" t="n">
-        <v>33</v>
+        <v>33.5</v>
       </c>
       <c r="H18" t="n">
-        <v>9</v>
+        <v>9.5</v>
       </c>
       <c r="I18" t="n">
-        <v>5</v>
+        <v>5.5</v>
       </c>
       <c r="J18" t="n">
         <v>27</v>
@@ -1605,10 +1605,10 @@
         <v>228</v>
       </c>
       <c r="R18" t="n">
-        <v>1.738</v>
+        <v>1.668</v>
       </c>
       <c r="S18" t="n">
-        <v>0.6175015428693976</v>
+        <v>0.598</v>
       </c>
     </row>
     <row r="19">
@@ -1634,16 +1634,16 @@
         </is>
       </c>
       <c r="F19" t="n">
-        <v>24</v>
+        <v>24.5</v>
       </c>
       <c r="G19" t="n">
-        <v>24</v>
+        <v>24.5</v>
       </c>
       <c r="H19" t="n">
-        <v>5</v>
+        <v>5.5</v>
       </c>
       <c r="I19" t="n">
-        <v>5</v>
+        <v>5.5</v>
       </c>
       <c r="J19" t="n">
         <v>45.5</v>
@@ -1675,7 +1675,7 @@
         <v>1</v>
       </c>
       <c r="S19" t="n">
-        <v>0.7108186533109109</v>
+        <v>0.6850000000000001</v>
       </c>
     </row>
     <row r="20">
@@ -1701,16 +1701,16 @@
         </is>
       </c>
       <c r="F20" t="n">
-        <v>36</v>
+        <v>36.5</v>
       </c>
       <c r="G20" t="n">
-        <v>33</v>
+        <v>33.5</v>
       </c>
       <c r="H20" t="n">
-        <v>21</v>
+        <v>21.5</v>
       </c>
       <c r="I20" t="n">
-        <v>9</v>
+        <v>9.5</v>
       </c>
       <c r="J20" t="n">
         <v>30.1</v>
@@ -1739,10 +1739,10 @@
         <v>12</v>
       </c>
       <c r="R20" t="n">
-        <v>3.733</v>
+        <v>3.621</v>
       </c>
       <c r="S20" t="n">
-        <v>0.5167818611982159</v>
+        <v>0.51</v>
       </c>
     </row>
     <row r="21">
@@ -1768,16 +1768,16 @@
         </is>
       </c>
       <c r="F21" t="n">
-        <v>68</v>
+        <v>68.5</v>
       </c>
       <c r="G21" t="n">
-        <v>64</v>
+        <v>64.5</v>
       </c>
       <c r="H21" t="n">
-        <v>35</v>
+        <v>35.5</v>
       </c>
       <c r="I21" t="n">
-        <v>34</v>
+        <v>34.5</v>
       </c>
       <c r="J21" t="n">
         <v>30</v>
@@ -1806,10 +1806,10 @@
         <v>34.5</v>
       </c>
       <c r="R21" t="n">
-        <v>0.9360000000000001</v>
+        <v>0.9350000000000001</v>
       </c>
       <c r="S21" t="n">
-        <v>0.3487399560040039</v>
+        <v>0.348</v>
       </c>
     </row>
   </sheetData>
